--- a/stories/arbres/ATOM-FAM.AID.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maël veut le livre des oiseaux. La boîte est en haut. Trop haut. C'est trop difficile. Maël va vers papa. Aller vers eux, c'est possible. Il dit le besoin. Maël dit : papa, j'ai besoin de la boîte. Papa écoute. Papa donne la boîte. Plus tard, dans la cuisine, le bocal est fermé. Maël se souvient. Il va vers maman. Il dit le besoin. Maël dit : maman, le bocal est trop dur. Maman tient le bocal avec lui. Le couvercle tourne. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
+          <t>Maël veut le livre des oiseaux. La boîte est en haut. Trop haut. C'est trop difficile. Maël va vers papa. Aller vers eux, c'est possible. Il dit le besoin. Papa, j'ai besoin de la boîte. Papa écoute. Papa donne la boîte. Plus tard, dans la cuisine, le bocal est fermé. Maël se souvient. Il va vers maman. Il dit le besoin. Maman, le bocal est trop dur. Maman tient le bocal avec lui. Le couvercle tourne. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maël veut le livre des oiseaux. La boîte est en haut. Trop haut. C'est trop difficile. Maël va vers papa. Aller vers eux, c'est possible. Il dit le besoin.
+enfant-m|Papa, j'ai besoin de la boîte. Papa écoute. Papa donne la boîte. Plus tard, dans la cuisine, le bocal est fermé.
+narrateur|Maël se souvient. Il va vers maman. Il dit le besoin.
+enfant-m|Maman, le bocal est trop dur. Maman tient le bocal avec lui.
+narrateur|Le couvercle tourne. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop difficile. Que fait Maël ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1659,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maël est allé vers papa. Puis vers maman. Il a dit le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1822,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maël ouvre le livre. Papa s'assoit près de lui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1989,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2029,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Le couvercle tourne. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|C'est trop difficile. Que fait Maël ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1664,6 +1671,7 @@
           <t>narrateur|Maël est allé vers papa. Puis vers maman. Il a dit le besoin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1835,7 @@
           <t>narrateur|Maël ouvre le livre. Papa s'assoit près de lui.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1994,6 +2003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2012,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2046,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2237,6 +2261,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.AID.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maël va vers papa et maman</t>
+          <t>Le pigeon de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un pigeon roucoule sur le toit. Raphaël veut le livre des oiseaux, trop haut. Il va vers papa et dit le besoin. Plus tard le bocal est dur. Il va vers maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maël veut le livre des oiseaux. La boîte est en haut. Trop haut. C'est trop difficile. Maël va vers papa. Aller vers eux, c'est possible. Il dit le besoin. Papa, j'ai besoin de la boîte. Papa écoute. Papa donne la boîte. Plus tard, dans la cuisine, le bocal est fermé. Maël se souvient. Il va vers maman. Il dit le besoin. Maman, le bocal est trop dur. Maman tient le bocal avec lui. Le couvercle tourne. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
+          <t>Un pigeon roucoule tout près du toit. Le rideau se soulève un peu. Une plume grise est collée à la vitre. La chambre sent le papier des livres. Un rayon de poussière danse au milieu. Le tapis bleu est un peu rêche. Papa plie un pull sur le lit. Maman chante tout bas, dans la cuisine. Tu entends le pigeon, Raphaël ? Il fait roucou. Oui. Comme dans ton livre. En ce moment, Raphaël cherche le livre des oiseaux. La boîte du livre est en haut. Trop haut. Le carton est beige, un peu poussiéreux. Je veux le livre, papa. Raphaël lève les bras. Il n'arrive pas. C'est trop difficile. Raphaël va vers papa. Aller vers eux, c'est possible. Il dit le besoin. Papa, j'ai besoin de la boîte. Elle est trop haute. Je t'écoute, Raphaël. Je te la donne. Papa donne la boîte. La boîte est un peu lourde. Merci, papa. Bravo. Tu as dit le besoin. Raphaël ouvre la boîte. Le livre sent le papier chaud. Un oiseau bleu est sur la couverture. C'est comme le pigeon. Presque. On le regardera. Plus tard, dans la cuisine, le bocal est fermé. Maman a mis des noisettes dedans. Raphaël se souvient. Il va vers maman. Il dit le besoin. Maman, le bocal est trop dur. J'ai besoin d'aide. Je t'écoute. On tient le bocal ensemble. Maman tient le bocal avec lui. Le couvercle tourne. Ça sent les noisettes. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible. J'ai dit le besoin. Oui. Bravo, Raphaël. Le pigeon roucoule encore, plus loin. La plume grise tremble un peu. On ouvre le livre, après le goûter ? Oui, papa. Une noisette roule dans la main de Raphaël. Elle est lisse et chaude.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,66 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maël veut le livre des oiseaux. La boîte est en haut. Trop haut. C'est trop difficile. Maël va vers papa. Aller vers eux, c'est possible. Il dit le besoin.
-enfant-m|Papa, j'ai besoin de la boîte. Papa écoute. Papa donne la boîte. Plus tard, dans la cuisine, le bocal est fermé.
-narrateur|Maël se souvient. Il va vers maman. Il dit le besoin.
-enfant-m|Maman, le bocal est trop dur. Maman tient le bocal avec lui.
-narrateur|Le couvercle tourne. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un pigeon roucoule tout près du toit.
+narrateur|Le rideau se soulève un peu.
+narrateur|Une plume grise est collée à la vitre.
+narrateur|La chambre sent le papier des livres.
+narrateur|Un rayon de poussière danse au milieu.
+narrateur|Le tapis bleu est un peu rêche.
+narrateur|Papa plie un pull sur le lit.
+narrateur|Maman chante tout bas, dans la cuisine.
+papa|Tu entends le pigeon, Raphaël ?
+enfant-m|Il fait roucou.
+papa|Oui. Comme dans ton livre.
+narrateur|En ce moment, Raphaël cherche le livre des oiseaux.
+narrateur|La boîte du livre est en haut.
+narrateur|Trop haut.
+narrateur|Le carton est beige, un peu poussiéreux.
+enfant-m|Je veux le livre, papa.
+narrateur|Raphaël lève les bras.
+narrateur|Il n'arrive pas.
+narrateur|C'est trop difficile.
+narrateur|Raphaël va vers papa.
+narrateur|Aller vers eux, c'est possible.
+narrateur|Il dit le besoin.
+enfant-m|Papa, j'ai besoin de la boîte.
+enfant-m|Elle est trop haute.
+papa|Je t'écoute, Raphaël.
+papa|Je te la donne.
+narrateur|Papa donne la boîte.
+narrateur|La boîte est un peu lourde.
+enfant-m|Merci, papa.
+papa|Bravo. Tu as dit le besoin.
+narrateur|Raphaël ouvre la boîte.
+narrateur|Le livre sent le papier chaud.
+narrateur|Un oiseau bleu est sur la couverture.
+enfant-m|C'est comme le pigeon.
+papa|Presque. On le regardera.
+narrateur|Plus tard, dans la cuisine, le bocal est fermé.
+narrateur|Maman a mis des noisettes dedans.
+narrateur|Raphaël se souvient.
+narrateur|Il va vers maman.
+narrateur|Il dit le besoin.
+enfant-m|Maman, le bocal est trop dur.
+enfant-m|J'ai besoin d'aide.
+maman|Je t'écoute.
+maman|On tient le bocal ensemble.
+narrateur|Maman tient le bocal avec lui.
+narrateur|Le couvercle tourne.
+narrateur|Ça sent les noisettes.
+maman|Quand c'est trop difficile, on va vers eux.
+papa|On dit le besoin.
+maman|Dire le besoin, c'est possible.
+enfant-m|J'ai dit le besoin.
+maman|Oui. Bravo, Raphaël.
+narrateur|Le pigeon roucoule encore, plus loin.
+narrateur|La plume grise tremble un peu.
+papa|On ouvre le livre, après le goûter ?
+enfant-m|Oui, papa.
+narrateur|Une noisette roule dans la main de Raphaël.
+narrateur|Elle est lisse et chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>C'est trop difficile. Que fait Maël ?</t>
+          <t>C'est trop difficile. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1564,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|C'est trop difficile. Que fait Maël ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|C'est trop difficile.
+narrateur|Que fait Raphaël ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maël est allé vers papa. Puis vers maman. Il a dit le besoin.</t>
+          <t>Raphaël est allé vers papa. Puis vers maman. Il a dit le besoin. Tu es venu me le dire. Bravo. Tu as dit : le bocal est trop dur. C'est du bon travail, Raphaël. Merci. L'oiseau bleu attend sur la couverture. Le pigeon se tait un moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1668,10 +1732,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maël est allé vers papa. Puis vers maman. Il a dit le besoin.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël est allé vers papa.
+narrateur|Puis vers maman.
+narrateur|Il a dit le besoin.
+papa|Tu es venu me le dire.
+papa|Bravo.
+maman|Tu as dit : le bocal est trop dur.
+maman|C'est du bon travail, Raphaël.
+enfant-m|Merci.
+narrateur|L'oiseau bleu attend sur la couverture.
+narrateur|Le pigeon se tait un moment.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1696,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maël ouvre le livre. Papa s'assoit près de lui.</t>
+          <t>Raphaël ouvre le livre. Papa s'assoit près de lui. Tu vois l'oiseau bleu ? Oui. Il a des plumes lisses. Tu as fini ta noisette ? Oui, maman. La page sent le papier. Elle est un peu rêche sous le doigt. On tourne la page ensemble ? Oui, papa. Le rideau se soulève encore. La plume grise reste à la vitre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1832,10 +1904,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maël ouvre le livre. Papa s'assoit près de lui.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël ouvre le livre.
+narrateur|Papa s'assoit près de lui.
+papa|Tu vois l'oiseau bleu ?
+enfant-m|Oui. Il a des plumes lisses.
+maman|Tu as fini ta noisette ?
+enfant-m|Oui, maman.
+narrateur|La page sent le papier.
+narrateur|Elle est un peu rêche sous le doigt.
+papa|On tourne la page ensemble ?
+enfant-m|Oui, papa.
+narrateur|Le rideau se soulève encore.
+narrateur|La plume grise reste à la vitre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1860,7 +1942,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers nous. Bravo, Raphaël. Tu as fait du bon travail. Le pigeon a fini de roucouler. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2000,10 +2082,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|J'ai dit le besoin.
+papa|Oui. Tu es venu vers nous.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+narrateur|Le pigeon a fini de roucouler.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2060,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-06.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maël veut le livre des oiseaux. La boîte est en haut. Trop haut. C'est trop difficile. Maël va vers papa. &lt;emphasis level="moderate"&gt;aller&lt;/emphasis&gt; vers eux, c'est possible. Il dit le besoin. Maël dit : papa, j'ai besoin de la boîte. Papa écoute. Papa donne la boîte. Plus tard, dans la cuisine, le bocal est fermé. Maël se souvient. Il va vers maman. Il dit le besoin. Maël dit : maman, le bocal est trop dur. Maman tient le bocal avec lui. Le couvercle tourne. Même leçon, autre lieu. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un pigeon roucoule tout près du toit. Le rideau se soulève un peu. Une plume grise est collée à la vitre. La chambre sent le papier des livres. Un rayon de poussière danse au milieu. Le tapis bleu est un peu rêche. Papa plie un pull sur le lit. Maman chante tout bas, dans la cuisine. Tu entends le pigeon, Raphaël ? Il fait roucou. Oui. Comme dans ton livre. En ce moment, Raphaël cherche le livre des oiseaux. La boîte du livre est en haut. Trop haut. Le carton est beige, un peu poussiéreux. Je veux le livre, papa. Raphaël lève les bras. Il n'arrive pas. C'est trop difficile. Raphaël va vers papa. Aller vers eux, c'est possible. Il dit le besoin. Papa, j'ai besoin de la boîte. Elle est trop haute. Je t'écoute, Raphaël. Je te la donne. Papa donne la boîte. La boîte est un peu lourde. Merci, papa. Bravo. Tu as dit le besoin. Raphaël ouvre la boîte. Le livre sent le papier chaud. Un oiseau bleu est sur la couverture. C'est comme le pigeon. Presque. On le regardera. Plus tard, dans la cuisine, le bocal est fermé. Maman a mis des noisettes dedans. Raphaël se souvient. Il va vers maman. Il dit le besoin. Maman, le bocal est trop dur. J'ai besoin d'aide. Je t'écoute. On tient le bocal ensemble. Maman tient le bocal avec lui. Le couvercle tourne. Ça sent les noisettes. Quand c'est trop difficile, on va vers eux. On dit le besoin. Dire le besoin, c'est possible. J'ai dit le besoin. Oui. Bravo, Raphaël. Le pigeon roucoule encore, plus loin. La plume grise tremble un peu. On ouvre le livre, après le goûter ? Oui, papa. Une noisette roule dans la main de Raphaël. Elle est lisse et chaude.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est trop difficile. Que fait Maël ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>C'est trop difficile. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est allé vers papa. Puis vers maman. Il a dit le besoin. Tu es venu me le dire. Bravo. Tu as dit : le bocal est trop dur. C'est du bon travail, Raphaël. Merci. L'oiseau bleu attend sur la couverture. Le pigeon se tait un moment.</t>
+          <t>Raphaël est allé vers papa. Puis vers maman. Il a dit le besoin. Tu es venu me le dire. Bravo. Tu as dit : le bocal est trop dur. Merci. L'oiseau bleu attend sur la couverture. Le pigeon se tait un moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maël est allé vers papa. Puis vers maman. Il a dit le besoin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël est allé vers papa. Puis vers maman. Il a dit le besoin. Tu es venu me le dire. Bravo. Tu as dit : le bocal est trop dur. Merci. L'oiseau bleu attend sur la couverture. Le pigeon se tait un moment.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1738,7 +1738,6 @@
 papa|Tu es venu me le dire.
 papa|Bravo.
 maman|Tu as dit : le bocal est trop dur.
-maman|C'est du bon travail, Raphaël.
 enfant-m|Merci.
 narrateur|L'oiseau bleu attend sur la couverture.
 narrateur|Le pigeon se tait un moment.</t>
@@ -1773,7 +1772,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maël ouvre le livre. Papa s'assoit près de lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël ouvre le livre. Papa s'assoit près de lui. Tu vois l'oiseau bleu ? Oui. Il a des plumes lisses. Tu as fini ta noisette ? Oui, maman. La page sent le papier. Elle est un peu rêche sous le doigt. On tourne la page ensemble ? Oui, papa. Le rideau se soulève encore. La plume grise reste à la vitre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le besoin. Oui. Tu es venu vers nous. Bravo, Raphaël. Tu as fait du bon travail. Le pigeon a fini de roucouler. L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers nous. Bravo, Raphaël. Le pigeon a fini de roucouler.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers nous. Bravo, Raphaël. Le pigeon a fini de roucouler.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2085,9 +2084,7 @@
           <t>enfant-m|J'ai dit le besoin.
 papa|Oui. Tu es venu vers nous.
 maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-narrateur|Le pigeon a fini de roucouler.
-narrateur|L'histoire est finie.</t>
+narrateur|Le pigeon a fini de roucouler.</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2150,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-06.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maël, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
